--- a/trading_signals/risk_management/risk_workbook_20260613_212317.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260613_212317.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-12  ·  Generated 2026-06-13T21:23:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-12  ·  Generated 2026-06-24T18:51:19  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.433</v>
+        <v>1.435</v>
       </c>
     </row>
     <row r="8">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>26.71</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.603</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8965</v>
+        <v>0.8969</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>5.67 / 2.83</t>
+          <t>5.74 / 2.87</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>KLAC (25.22% NAV)</t>
+          <t>KLAC (25.25% NAV)</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>26.71</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="7">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-82451.39999999999</v>
+        <v>-82449.17</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-7.17</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="5">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-164902.81</v>
+        <v>-164898.33</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-14.33</v>
+        <v>-14.35</v>
       </c>
     </row>
     <row r="6">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-82451.39999999999</v>
+        <v>-82449.17</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-7.17</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="7">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="D6" s="30" t="n">
         <v>3</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>25.22</v>
+        <v>25.25</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>24.92</v>
+        <v>24.95</v>
       </c>
       <c r="D9" s="34" t="n">
         <v>15</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>15.23</v>
+        <v>15.25</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>15</v>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -3304,16 +3304,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>12.2</v>
+        <v>14.16</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-12.07</v>
+        <v>-13.57</v>
       </c>
     </row>
     <row r="7">
@@ -3323,16 +3323,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>12.83</v>
+        <v>14.55</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>8.050000000000001</v>
+        <v>27.64</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>-4.78</v>
+      <c r="E7" s="20" t="n">
+        <v>13.09</v>
       </c>
     </row>
     <row r="8">
@@ -3342,16 +3342,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>21.22</v>
+        <v>24.36</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1.56</v>
+        <v>3.77</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-19.65</v>
+        <v>-20.59</v>
       </c>
     </row>
     <row r="9">
@@ -3361,16 +3361,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>53.76</v>
+        <v>46.93</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>90.25</v>
+        <v>68</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>36.5</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="11">
@@ -3580,30 +3580,30 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>38.82</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.004 (t=0.04)</t>
+          <t>0.003 (t=0.04)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>-0.077 (t=-0.56)</t>
+          <t>-0.075 (t=-0.55)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>0.074 (t=0.61)</t>
+          <t>0.073 (t=0.6)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.109 (t=-0.61)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -3629,45 +3629,45 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>45.76</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>116</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.076 (t=0.51)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.139 (t=-0.61)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.053 (t=-0.26)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.26 (t=1.36)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.215 (t=-0.71)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>-0.145 (t=-1.35)</t>
+          <t>-0.141 (t=-1.36)</t>
         </is>
       </c>
     </row>
@@ -3678,45 +3678,45 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>31.8</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.096 (t=-0.54)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>0.029 (t=0.1)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.226 (t=0.92)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.128 (t=-0.56)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.033 (t=0.09)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.059 (t=-0.45)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.847</v>
+        <v>0.825</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>21.189</v>
+        <v>20.982</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -3817,10 +3817,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.405</v>
+        <v>2.379</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.405</v>
+        <v>2.379</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.71</v>
+        <v>-0.418</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>3.897</v>
+        <v>2.568</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -3845,13 +3845,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.643</v>
+        <v>1.588</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.761</v>
+        <v>1.653</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.118</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="6">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.955</v>
+        <v>1.951</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>23.461</v>
+        <v>24.079</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -3873,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5.138</v>
+        <v>5.107</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>5.138</v>
+        <v>5.107</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -3941,31 +3941,31 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.603</v>
+        <v>1.608</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8965</v>
+        <v>0.8969</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>74.7</v>
+        <v>75.3</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>5.67</v>
+        <v>5.74</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
     </row>
     <row r="10">
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.042</v>
+        <v>1.18</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.7849</v>
+        <v>0.8158</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>662</v>
+        <v>509</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>9.31</v>
@@ -3993,10 +3993,10 @@
         <v>77.3</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>4.48</v>
+        <v>5.41</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>0</v>
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.382</v>
+        <v>1.346</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.8739</v>
+        <v>0.8672</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -4027,13 +4027,13 @@
         <v>78.59999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.464</v>
+        <v>2.497</v>
       </c>
     </row>
   </sheetData>
@@ -4108,16 +4108,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>107077.31</v>
+        <v>105442.27</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>345575.99</v>
+        <v>344117.58</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>439264.74</v>
+        <v>439856.38</v>
       </c>
     </row>
     <row r="6">
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1569451.93</v>
+        <v>1567816.89</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1491802.71</v>
+        <v>1490344.3</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>2652712.4</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1674090.61</v>
+        <v>1674682.25</v>
       </c>
     </row>
     <row r="9">
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>842542.91</v>
+        <v>842219.7</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>354415.58</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1645833.84</v>
+        <v>1645510.63</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>663371.0699999999</v>
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1137387.13</v>
+        <v>1135928.72</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1006878.56</v>
+        <v>1007201.77</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1010719.54</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="13">
@@ -4260,16 +4260,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1.002</v>
+        <v>1.003</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.619</v>
+        <v>2.618</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.209</v>
+        <v>1.208</v>
       </c>
     </row>
     <row r="14">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>1.023</v>
@@ -4317,16 +4317,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>859952.2</v>
+        <v>858317.16</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>909559.45</v>
+        <v>908101.04</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>479549.24</v>
+        <v>479872.45</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>766407.85</v>
+        <v>766999.49</v>
       </c>
     </row>
     <row r="17">
@@ -4395,7 +4395,7 @@
         <v>784722.83</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1006878.56</v>
+        <v>1007201.77</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>558187.38</v>
@@ -4452,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>826477.09</v>
+        <v>826153.88</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>784722.83</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1006878.56</v>
+        <v>1007201.77</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>558187.38</v>
@@ -4598,16 +4598,16 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>107077.31</v>
+        <v>105442.27</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>345575.99</v>
+        <v>344117.58</v>
       </c>
       <c r="D32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>439264.74</v>
+        <v>439856.38</v>
       </c>
     </row>
     <row r="33">
@@ -4617,16 +4617,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1137387.13</v>
+        <v>1135928.72</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1006878.56</v>
+        <v>1007201.77</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1010719.54</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="34">
@@ -4689,16 +4689,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>475463.57</v>
+        <v>481651.58</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>317071.39</v>
+        <v>323404.31</v>
       </c>
     </row>
     <row r="40">
@@ -4746,16 +4746,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>650069.42</v>
+        <v>656257.4300000001</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>861250.61</v>
+        <v>867583.53</v>
       </c>
     </row>
     <row r="43">
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>563108.77</v>
+        <v>569296.78</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>576295.8100000001</v>
+        <v>582628.73</v>
       </c>
     </row>
     <row r="47">
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.307</v>
+        <v>0.304</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="48">
@@ -4869,7 +4869,7 @@
         <v>-0.002</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>-0.055</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="49">
@@ -4898,16 +4898,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>528535.4399999999</v>
+        <v>534723.45</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>468599.79</v>
+        <v>474932.71</v>
       </c>
     </row>
     <row r="51">
@@ -5179,16 +5179,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>475463.57</v>
+        <v>481651.58</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>317071.39</v>
+        <v>323404.31</v>
       </c>
     </row>
     <row r="67">
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>563108.77</v>
+        <v>569296.78</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>576295.8100000001</v>
+        <v>582628.73</v>
       </c>
     </row>
     <row r="68">
@@ -5279,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>122193.34</v>
+        <v>116452.06</v>
       </c>
     </row>
     <row r="74">
@@ -5336,7 +5336,7 @@
         <v>2478106.55</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>812840</v>
+        <v>807098.72</v>
       </c>
     </row>
     <row r="77">
@@ -5365,13 +5365,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>453683.23</v>
+        <v>461480.48</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>215184.56</v>
+        <v>222805.18</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1318006.48</v>
+        <v>1323871.28</v>
       </c>
       <c r="E78" s="15" t="n">
         <v>0</v>
@@ -5384,13 +5384,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>872382.83</v>
+        <v>880180.08</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>569600.14</v>
+        <v>577220.76</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2034336.76</v>
+        <v>2040201.56</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>378416.27</v>
@@ -5403,16 +5403,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>576626.58</v>
+        <v>569005.96</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>443769.79</v>
+        <v>437904.99</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>434423.73</v>
+        <v>428682.45</v>
       </c>
     </row>
     <row r="81">
@@ -5422,16 +5422,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2.464</v>
+        <v>2.497</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>1.976</v>
+        <v>2.002</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>5.552</v>
+        <v>5.626</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1.572</v>
+        <v>1.593</v>
       </c>
     </row>
     <row r="82">
@@ -5441,16 +5441,16 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>1.045</v>
+        <v>1.059</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>0.746</v>
+        <v>0.756</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>2.324</v>
+        <v>2.355</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.17</v>
+        <v>-0.172</v>
       </c>
     </row>
     <row r="83">
@@ -5479,16 +5479,16 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>299191.66</v>
+        <v>291394.41</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>348798.9</v>
+        <v>341178.28</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-48986.2</v>
+        <v>-54851</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>297808.06</v>
+        <v>292066.78</v>
       </c>
     </row>
     <row r="85">
@@ -5501,13 +5501,13 @@
         <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="7" t="n">
         <v>-0</v>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>576626.58</v>
+        <v>569005.96</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>443769.79</v>
+        <v>437904.99</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>304662.06</v>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>445309.24</v>
+        <v>453106.49</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>208096.25</v>
+        <v>215716.87</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>1303679.87</v>
+        <v>1309544.67</v>
       </c>
       <c r="E92" s="15" t="n">
         <v>0</v>
@@ -5627,13 +5627,13 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>576626.58</v>
+        <v>569005.96</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>443769.79</v>
+        <v>437904.99</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>304662.06</v>
@@ -5766,10 +5766,10 @@
         <v>0</v>
       </c>
       <c r="D100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>122193.34</v>
+        <v>116452.06</v>
       </c>
     </row>
     <row r="101">
@@ -5779,16 +5779,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>576626.58</v>
+        <v>569005.96</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>443769.79</v>
+        <v>437904.99</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>434423.73</v>
+        <v>428682.45</v>
       </c>
     </row>
     <row r="102">
@@ -5882,16 +5882,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>13365.2</v>
+        <v>13188.57</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>143873.77</v>
+        <v>141915.52</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>140032.79</v>
+        <v>137806.11</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>229253.54</v>
+        <v>227618.5</v>
       </c>
     </row>
     <row r="6">
@@ -5967,13 +5967,13 @@
         <v>0</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>-2348.22</v>
+        <v>-2374.03</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-15535.26</v>
+        <v>-15705.98</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>51428.61</v>
+        <v>57590.81</v>
       </c>
     </row>
     <row r="12">
@@ -6046,16 +6046,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>13365.21</v>
+        <v>13188.58</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>146222</v>
+        <v>144289.55</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>155568.06</v>
+        <v>153512.09</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>177824.94</v>
+        <v>170027.69</v>
       </c>
     </row>
     <row r="18">
@@ -6065,16 +6065,16 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>62.15</v>
+        <v>63.22</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>310.74</v>
+        <v>316.08</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1305.12</v>
+        <v>1327.55</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>9570.85</v>
+        <v>9735.34</v>
       </c>
     </row>
     <row r="19">
@@ -6166,13 +6166,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1137387.13</v>
+        <v>1135928.72</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1006878.56</v>
+        <v>1007201.77</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1010719.54</v>
+        <v>1011311.18</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -6185,16 +6185,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>13365.2</v>
+        <v>13188.57</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>143873.77</v>
+        <v>141915.52</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>140032.79</v>
+        <v>137806.11</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>229253.54</v>
+        <v>227618.5</v>
       </c>
     </row>
     <row r="7">
@@ -6242,16 +6242,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
     </row>
     <row r="10">
@@ -6261,16 +6261,16 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>14.29</v>
+        <v>14.09</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>13.85</v>
+        <v>13.63</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>24.88</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="11">
@@ -6286,10 +6286,10 @@
         <v>-0.87</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-9.52</v>
+        <v>-9.41</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-9.52</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6333,13 +6333,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>563108.77</v>
+        <v>569296.78</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>576295.8100000001</v>
+        <v>582628.73</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6355,13 +6355,13 @@
         <v>0</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-2348.22</v>
+        <v>-2374.03</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-15535.26</v>
+        <v>-15705.98</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>51428.61</v>
+        <v>57590.81</v>
       </c>
     </row>
     <row r="17">
@@ -6409,16 +6409,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
     </row>
     <row r="20">
@@ -6437,7 +6437,7 @@
         <v>-2.7</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>10.1</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="21">
@@ -6500,13 +6500,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>576626.58</v>
+        <v>569005.96</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>443769.79</v>
+        <v>437904.99</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>434423.73</v>
+        <v>428682.45</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6519,16 +6519,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>13365.21</v>
+        <v>13188.58</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>146222</v>
+        <v>144289.55</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>155568.06</v>
+        <v>153512.09</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>177824.94</v>
+        <v>170027.69</v>
       </c>
     </row>
     <row r="27">
@@ -6576,16 +6576,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
     </row>
     <row r="30">
@@ -6604,7 +6604,7 @@
         <v>35.81</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>43.14</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="31">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>143873.77</v>
+        <v>141915.52</v>
       </c>
     </row>
     <row r="5">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-842542.91</v>
+        <v>-842219.7</v>
       </c>
     </row>
     <row r="7">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>-285205.86</v>
+        <v>-286840.9</v>
       </c>
     </row>
     <row r="8">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>107077.31</v>
+        <v>105442.27</v>
       </c>
     </row>
     <row r="11">
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011103.74</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025051.32</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026690.72</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015359.98</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003162.43</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013277.95</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1027021.03</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1054148.08</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1051498.27</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1050078.94</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049591.92</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1043241.05</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1049025.46</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1043117.12</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044635.34</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070736.97</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061826.91</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074933.41</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080449.67</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086715.78</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -7900,7 +7900,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071892.67</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065502.29</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080379.78</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075233.42</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1070583.4</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073148.35</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1073704.08</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1083942.34</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1084938.93</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092024.86</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092149.17</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1052087.23</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1048464.49</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1042951.71</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1031548.19</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1038690.65</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1036595.47</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1018492.18</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1013499.62</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>998793.52</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1010719.54</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1013792.37</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011137.79</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>997749.49</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1013932.08</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023020.78</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023350.89</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996212.58</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016375.33</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997437.28</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>990840.4</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>988548.85</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004260.13</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1100523.26</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1109402.67</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="151">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1112817.28</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="152">
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1006878.56</v>
+        <v>1007201.77</v>
       </c>
     </row>
     <row r="153">
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="B153" s="13" t="n">
-        <v>1064254.6</v>
+        <v>1063800.8</v>
       </c>
     </row>
     <row r="154">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>1056068.38</v>
+        <v>1055689.39</v>
       </c>
     </row>
     <row r="155">
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="B155" s="13" t="n">
-        <v>1054947.53</v>
+        <v>1054547.31</v>
       </c>
     </row>
     <row r="156">
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="B156" s="4" t="n">
-        <v>1137387.13</v>
+        <v>1135928.72</v>
       </c>
     </row>
     <row r="157">
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="B157" s="13" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
     </row>
   </sheetData>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1150752.33</v>
+        <v>1149117.29</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1035301.03</v>
@@ -8430,16 +8430,16 @@
         <v>616601.4300000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>126.35</v>
+        <v>126.53</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>63.18</v>
+        <v>63.27</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>8</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>560760.55</v>
+        <v>566922.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>589991.79</v>
+        <v>582194.54</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1035301.03</v>
@@ -8504,16 +8504,16 @@
         <v>616601.4300000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.464</v>
+        <v>2.497</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.045</v>
+        <v>1.059</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>246.44</v>
+        <v>249.74</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>123.22</v>
+        <v>124.87</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>8</v>
@@ -8603,7 +8603,7 @@
         <v>290175.6</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>25.22</v>
+        <v>25.25</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>19.96</v>
@@ -8625,7 +8625,7 @@
         <v>286718.64</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>24.92</v>
+        <v>24.95</v>
       </c>
       <c r="E7" s="20" t="n">
         <v>19.72</v>
@@ -8647,7 +8647,7 @@
         <v>175280.25</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>15.23</v>
+        <v>15.25</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>12.06</v>
@@ -8669,7 +8669,7 @@
         <v>-122923.96</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>10.68</v>
+        <v>10.7</v>
       </c>
       <c r="E9" s="20" t="n">
         <v>8.449999999999999</v>
@@ -8691,7 +8691,7 @@
         <v>98671.89</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>8.57</v>
+        <v>8.59</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>6.79</v>
@@ -8713,7 +8713,7 @@
         <v>96825.5</v>
       </c>
       <c r="D11" s="20" t="n">
-        <v>8.41</v>
+        <v>8.43</v>
       </c>
       <c r="E11" s="20" t="n">
         <v>6.66</v>
@@ -8735,7 +8735,7 @@
         <v>87629.14999999999</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>7.61</v>
+        <v>7.63</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>6.03</v>
@@ -8757,7 +8757,7 @@
         <v>-81089.55</v>
       </c>
       <c r="D13" s="20" t="n">
-        <v>7.05</v>
+        <v>7.06</v>
       </c>
       <c r="E13" s="20" t="n">
         <v>5.58</v>
@@ -8801,7 +8801,7 @@
         <v>-51015.58</v>
       </c>
       <c r="D15" s="20" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="E15" s="20" t="n">
         <v>3.51</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.433</v>
+        <v>1.435</v>
       </c>
     </row>
     <row r="4">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.143</v>
+        <v>2.146</v>
       </c>
     </row>
     <row r="5">
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>53.58</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="6">

--- a/trading_signals/risk_management/risk_workbook_20260613_212317.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260613_212317.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-12  ·  Generated 2026-06-24T18:51:19  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-12  ·  Generated 2026-06-25T01:49:52  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
         <v>105442.27</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>344117.58</v>
+        <v>196692.32</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         <v>427073.59</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>361503.89</v>
+        <v>416204.88</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>819356.75</v>
@@ -4149,7 +4149,7 @@
         <v>1035301.03</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>784722.83</v>
+        <v>931075.52</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1833355.65</v>
@@ -4168,7 +4168,7 @@
         <v>1567816.89</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1490344.3</v>
+        <v>1543972.72</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>2652712.4</v>
@@ -4187,7 +4187,7 @@
         <v>418699.6</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>803290.9399999999</v>
@@ -4225,7 +4225,7 @@
         <v>418699.6</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>1645510.63</v>
@@ -4263,7 +4263,7 @@
         <v>1.265</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1.003</v>
+        <v>1.179</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2.618</v>
@@ -4282,7 +4282,7 @@
         <v>0.537</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.379</v>
+        <v>0.46</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>1.023</v>
@@ -4301,7 +4301,7 @@
         <v>290800.13</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>227827.68</v>
+        <v>267823.9</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>527329.3199999999</v>
@@ -4320,7 +4320,7 @@
         <v>858317.16</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>908101.04</v>
+        <v>868104.8199999999</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>479872.45</v>
@@ -4392,7 +4392,7 @@
         <v>1035301.03</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>784722.83</v>
+        <v>931075.52</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>1007201.77</v>
@@ -4430,7 +4430,7 @@
         <v>1035301.03</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>784722.83</v>
+        <v>931075.52</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1833355.65</v>
@@ -4468,7 +4468,7 @@
         <v>1035301.03</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>784722.83</v>
+        <v>931075.52</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>1007201.77</v>
@@ -4487,7 +4487,7 @@
         <v>8373.99</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>7088.31</v>
+        <v>8160.88</v>
       </c>
       <c r="D26" s="15" t="n">
         <v>0</v>
@@ -4506,7 +4506,7 @@
         <v>8373.99</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7088.31</v>
+        <v>8160.88</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>0</v>
@@ -4525,7 +4525,7 @@
         <v>418699.6</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>803290.9399999999</v>
@@ -4544,7 +4544,7 @@
         <v>418699.6</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>803290.9399999999</v>
@@ -4582,7 +4582,7 @@
         <v>8373.99</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7088.31</v>
+        <v>8160.88</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>105442.27</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>344117.58</v>
+        <v>196692.32</v>
       </c>
       <c r="D32" s="15" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>427073.59</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>361503.89</v>
+        <v>416204.88</v>
       </c>
       <c r="D74" s="13" t="n">
         <v>730656.89</v>
@@ -5311,7 +5311,7 @@
         <v>1035301.03</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>784722.83</v>
+        <v>931075.52</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>1747449.66</v>
@@ -5330,7 +5330,7 @@
         <v>1462374.62</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>1146226.72</v>
+        <v>1347280.4</v>
       </c>
       <c r="D76" s="13" t="n">
         <v>2478106.55</v>
@@ -5349,7 +5349,7 @@
         <v>418699.6</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>716330.29</v>
@@ -5368,7 +5368,7 @@
         <v>461480.48</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>222805.18</v>
+        <v>370230.44</v>
       </c>
       <c r="D78" s="13" t="n">
         <v>1323871.28</v>
@@ -5387,7 +5387,7 @@
         <v>880180.08</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>577220.76</v>
+        <v>778274.4399999999</v>
       </c>
       <c r="D79" s="4" t="n">
         <v>2040201.56</v>
@@ -5425,7 +5425,7 @@
         <v>2.497</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>2.002</v>
+        <v>2.353</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>5.626</v>
@@ -5444,7 +5444,7 @@
         <v>1.059</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>0.756</v>
+        <v>0.919</v>
       </c>
       <c r="D82" s="17" t="n">
         <v>2.355</v>
@@ -5463,7 +5463,7 @@
         <v>290800.13</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>227827.68</v>
+        <v>267823.9</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>492755.99</v>
@@ -5482,7 +5482,7 @@
         <v>291394.41</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>341178.28</v>
+        <v>301182.06</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>-54851</v>
@@ -5592,7 +5592,7 @@
         <v>1035301.03</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>784722.83</v>
+        <v>931075.52</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>1747449.66</v>
@@ -5611,7 +5611,7 @@
         <v>453106.49</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>215716.87</v>
+        <v>362069.56</v>
       </c>
       <c r="D92" s="13" t="n">
         <v>1309544.67</v>
@@ -5687,7 +5687,7 @@
         <v>418699.6</v>
       </c>
       <c r="C96" s="13" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D96" s="13" t="n">
         <v>716330.29</v>
@@ -5706,7 +5706,7 @@
         <v>418699.6</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>354415.58</v>
+        <v>408044</v>
       </c>
       <c r="D97" s="4" t="n">
         <v>716330.29</v>
@@ -5725,7 +5725,7 @@
         <v>8373.99</v>
       </c>
       <c r="C98" s="13" t="n">
-        <v>7088.31</v>
+        <v>8160.88</v>
       </c>
       <c r="D98" s="13" t="n">
         <v>14326.61</v>
